--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129717877</v>
       </c>
       <c r="B2" t="n">
-        <v>92881</v>
+        <v>92882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129722137</v>
       </c>
       <c r="B3" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129722133</v>
+        <v>129717830</v>
       </c>
       <c r="B4" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,14 +910,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Rickeby, Upl</t>
+          <t>Runsten, Runsten, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681041</v>
+        <v>680855</v>
       </c>
       <c r="R4" t="n">
-        <v>6625412</v>
+        <v>6625471</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,9 +947,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129717830</v>
+        <v>129722133</v>
       </c>
       <c r="B5" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Runsten, Runsten, Upl</t>
+          <t>Östra Rickeby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680855</v>
+        <v>681041</v>
       </c>
       <c r="R5" t="n">
-        <v>6625471</v>
+        <v>6625412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,19 +1054,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>129722132</v>
       </c>
       <c r="B6" t="n">
-        <v>92881</v>
+        <v>92882</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129722136</v>
       </c>
       <c r="B7" t="n">
-        <v>92881</v>
+        <v>92882</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129722134</v>
       </c>
       <c r="B8" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129722139</v>
       </c>
       <c r="B9" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129722136</v>
+        <v>129722139</v>
       </c>
       <c r="B7" t="n">
-        <v>92882</v>
+        <v>100958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
         <v>681092</v>
       </c>
       <c r="R7" t="n">
-        <v>6625387</v>
+        <v>6625222</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129722134</v>
+        <v>129722136</v>
       </c>
       <c r="B8" t="n">
-        <v>100958</v>
+        <v>92882</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681046</v>
+        <v>681092</v>
       </c>
       <c r="R8" t="n">
-        <v>6625408</v>
+        <v>6625387</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129722139</v>
+        <v>129722134</v>
       </c>
       <c r="B9" t="n">
         <v>100958</v>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>681092</v>
+        <v>681046</v>
       </c>
       <c r="R9" t="n">
-        <v>6625222</v>
+        <v>6625408</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129717877</v>
       </c>
       <c r="B2" t="n">
-        <v>92882</v>
+        <v>92887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129717830</v>
       </c>
       <c r="B4" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129722133</v>
       </c>
       <c r="B5" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129722132</v>
       </c>
       <c r="B6" t="n">
-        <v>92882</v>
+        <v>92887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129722139</v>
+        <v>129722136</v>
       </c>
       <c r="B7" t="n">
-        <v>100958</v>
+        <v>92887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
         <v>681092</v>
       </c>
       <c r="R7" t="n">
-        <v>6625222</v>
+        <v>6625387</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129722136</v>
+        <v>129722134</v>
       </c>
       <c r="B8" t="n">
-        <v>92882</v>
+        <v>100963</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681092</v>
+        <v>681046</v>
       </c>
       <c r="R8" t="n">
-        <v>6625387</v>
+        <v>6625408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129722134</v>
+        <v>129722139</v>
       </c>
       <c r="B9" t="n">
-        <v>100958</v>
+        <v>100963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>681046</v>
+        <v>681092</v>
       </c>
       <c r="R9" t="n">
-        <v>6625408</v>
+        <v>6625222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129717877</v>
       </c>
       <c r="B2" t="n">
-        <v>92887</v>
+        <v>92891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129717830</v>
       </c>
       <c r="B4" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129722133</v>
       </c>
       <c r="B5" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129722132</v>
       </c>
       <c r="B6" t="n">
-        <v>92887</v>
+        <v>92891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129722136</v>
       </c>
       <c r="B7" t="n">
-        <v>92887</v>
+        <v>92891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129722134</v>
       </c>
       <c r="B8" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129722139</v>
       </c>
       <c r="B9" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129717877</v>
       </c>
       <c r="B2" t="n">
-        <v>92891</v>
+        <v>92893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129717830</v>
       </c>
       <c r="B4" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129722133</v>
       </c>
       <c r="B5" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129722132</v>
       </c>
       <c r="B6" t="n">
-        <v>92891</v>
+        <v>92893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129722136</v>
       </c>
       <c r="B7" t="n">
-        <v>92891</v>
+        <v>92893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129722134</v>
       </c>
       <c r="B8" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129722139</v>
       </c>
       <c r="B9" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129722136</v>
+        <v>129722134</v>
       </c>
       <c r="B7" t="n">
-        <v>92893</v>
+        <v>100969</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681092</v>
+        <v>681046</v>
       </c>
       <c r="R7" t="n">
-        <v>6625387</v>
+        <v>6625408</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129722134</v>
+        <v>129722139</v>
       </c>
       <c r="B8" t="n">
         <v>100969</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681046</v>
+        <v>681092</v>
       </c>
       <c r="R8" t="n">
-        <v>6625408</v>
+        <v>6625222</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129722139</v>
+        <v>129722136</v>
       </c>
       <c r="B9" t="n">
-        <v>100969</v>
+        <v>92893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         <v>681092</v>
       </c>
       <c r="R9" t="n">
-        <v>6625222</v>
+        <v>6625387</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129722134</v>
+        <v>129722136</v>
       </c>
       <c r="B7" t="n">
-        <v>100969</v>
+        <v>92893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681046</v>
+        <v>681092</v>
       </c>
       <c r="R7" t="n">
-        <v>6625408</v>
+        <v>6625387</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129722139</v>
+        <v>129722134</v>
       </c>
       <c r="B8" t="n">
         <v>100969</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681092</v>
+        <v>681046</v>
       </c>
       <c r="R8" t="n">
-        <v>6625222</v>
+        <v>6625408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129722136</v>
+        <v>129722139</v>
       </c>
       <c r="B9" t="n">
-        <v>92893</v>
+        <v>100969</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         <v>681092</v>
       </c>
       <c r="R9" t="n">
-        <v>6625387</v>
+        <v>6625222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>129717830</v>
       </c>
       <c r="B4" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129722133</v>
       </c>
       <c r="B5" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129722134</v>
       </c>
       <c r="B8" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129722139</v>
       </c>
       <c r="B9" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129717877</v>
       </c>
       <c r="B2" t="n">
-        <v>92893</v>
+        <v>92896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129722137</v>
       </c>
       <c r="B3" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129717830</v>
       </c>
       <c r="B4" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129722133</v>
       </c>
       <c r="B5" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129722132</v>
       </c>
       <c r="B6" t="n">
-        <v>92893</v>
+        <v>92896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129722136</v>
       </c>
       <c r="B7" t="n">
-        <v>92893</v>
+        <v>92896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129722134</v>
       </c>
       <c r="B8" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129722139</v>
       </c>
       <c r="B9" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129722136</v>
+        <v>129722134</v>
       </c>
       <c r="B7" t="n">
-        <v>92896</v>
+        <v>100983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681092</v>
+        <v>681046</v>
       </c>
       <c r="R7" t="n">
-        <v>6625387</v>
+        <v>6625408</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129722134</v>
+        <v>129722139</v>
       </c>
       <c r="B8" t="n">
         <v>100983</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681046</v>
+        <v>681092</v>
       </c>
       <c r="R8" t="n">
-        <v>6625408</v>
+        <v>6625222</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129722139</v>
+        <v>129722136</v>
       </c>
       <c r="B9" t="n">
-        <v>100983</v>
+        <v>92896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         <v>681092</v>
       </c>
       <c r="R9" t="n">
-        <v>6625222</v>
+        <v>6625387</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129717877</v>
       </c>
       <c r="B2" t="n">
-        <v>92896</v>
+        <v>92899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129722137</v>
       </c>
       <c r="B3" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>129717830</v>
       </c>
       <c r="B4" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129722133</v>
       </c>
       <c r="B5" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>129722132</v>
       </c>
       <c r="B6" t="n">
-        <v>92896</v>
+        <v>92899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129722134</v>
+        <v>129722136</v>
       </c>
       <c r="B7" t="n">
-        <v>100983</v>
+        <v>92899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681046</v>
+        <v>681092</v>
       </c>
       <c r="R7" t="n">
-        <v>6625408</v>
+        <v>6625387</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129722139</v>
+        <v>129722134</v>
       </c>
       <c r="B8" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681092</v>
+        <v>681046</v>
       </c>
       <c r="R8" t="n">
-        <v>6625222</v>
+        <v>6625408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129722136</v>
+        <v>129722139</v>
       </c>
       <c r="B9" t="n">
-        <v>92896</v>
+        <v>100986</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         <v>681092</v>
       </c>
       <c r="R9" t="n">
-        <v>6625387</v>
+        <v>6625222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129717877</v>
       </c>
       <c r="B2" t="n">
-        <v>92899</v>
+        <v>92900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129717830</v>
+        <v>129722133</v>
       </c>
       <c r="B4" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,14 +910,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Runsten, Runsten, Upl</t>
+          <t>Östra Rickeby, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680855</v>
+        <v>681041</v>
       </c>
       <c r="R4" t="n">
-        <v>6625471</v>
+        <v>6625412</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,19 +947,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129722133</v>
+        <v>129717830</v>
       </c>
       <c r="B5" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,14 +1007,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östra Rickeby, Upl</t>
+          <t>Runsten, Runsten, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681041</v>
+        <v>680855</v>
       </c>
       <c r="R5" t="n">
-        <v>6625412</v>
+        <v>6625471</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,9 +1044,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>129722132</v>
       </c>
       <c r="B6" t="n">
-        <v>92899</v>
+        <v>92900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129722136</v>
+        <v>129722134</v>
       </c>
       <c r="B7" t="n">
-        <v>92899</v>
+        <v>100987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681092</v>
+        <v>681046</v>
       </c>
       <c r="R7" t="n">
-        <v>6625387</v>
+        <v>6625408</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,17 +1270,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129722134</v>
+        <v>129722139</v>
       </c>
       <c r="B8" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681046</v>
+        <v>681092</v>
       </c>
       <c r="R8" t="n">
-        <v>6625408</v>
+        <v>6625222</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129722139</v>
+        <v>129722136</v>
       </c>
       <c r="B9" t="n">
-        <v>100986</v>
+        <v>92900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         <v>681092</v>
       </c>
       <c r="R9" t="n">
-        <v>6625222</v>
+        <v>6625387</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 47212-2025 artfynd.xlsx
+++ b/artfynd/A 47212-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129717877</v>
       </c>
       <c r="B2" t="n">
-        <v>92900</v>
+        <v>92917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +785,7 @@
         <v>129722137</v>
       </c>
       <c r="B3" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129722133</v>
+        <v>129717830</v>
       </c>
       <c r="B4" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,14 +910,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östra Rickeby, Upl</t>
+          <t>Runsten, Runsten, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681041</v>
+        <v>680855</v>
       </c>
       <c r="R4" t="n">
-        <v>6625412</v>
+        <v>6625471</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,9 +947,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129717830</v>
+        <v>129722133</v>
       </c>
       <c r="B5" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,14 +1017,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Runsten, Runsten, Upl</t>
+          <t>Östra Rickeby, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680855</v>
+        <v>681041</v>
       </c>
       <c r="R5" t="n">
-        <v>6625471</v>
+        <v>6625412</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,19 +1054,9 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:08</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,7 +1071,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1086,7 +1086,7 @@
         <v>129722132</v>
       </c>
       <c r="B6" t="n">
-        <v>92900</v>
+        <v>92917</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129722134</v>
+        <v>129722136</v>
       </c>
       <c r="B7" t="n">
-        <v>100987</v>
+        <v>92917</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681046</v>
+        <v>681092</v>
       </c>
       <c r="R7" t="n">
-        <v>6625408</v>
+        <v>6625387</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129722139</v>
+        <v>129722134</v>
       </c>
       <c r="B8" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>681092</v>
+        <v>681046</v>
       </c>
       <c r="R8" t="n">
-        <v>6625222</v>
+        <v>6625408</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129722136</v>
+        <v>129722139</v>
       </c>
       <c r="B9" t="n">
-        <v>92900</v>
+        <v>101004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1412,7 +1412,7 @@
         <v>681092</v>
       </c>
       <c r="R9" t="n">
-        <v>6625387</v>
+        <v>6625222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
